--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
   <si>
     <t>选手ID</t>
   </si>
@@ -38,9 +38,6 @@
   </si>
   <si>
     <t>负场</t>
-  </si>
-  <si>
-    <t>KDA</t>
   </si>
   <si>
     <t>最后比赛时间</t>
@@ -983,13 +980,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="4"/>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="3"/>
   <cols>
-    <col min="5" max="5" width="14.25" customWidth="1"/>
+    <col min="4" max="4" width="14.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1002,13 +999,10 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
         <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" t="s">
-        <v>5</v>
       </c>
       <c r="B2">
         <v>12</v>
@@ -1016,16 +1010,13 @@
       <c r="C2">
         <v>2</v>
       </c>
-      <c r="D2">
-        <v>4.5</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
-        <v>7</v>
       </c>
       <c r="B3">
         <v>9</v>
@@ -1033,11 +1024,8 @@
       <c r="C3">
         <v>3</v>
       </c>
-      <c r="D3">
-        <v>4</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
+      <c r="D3" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -27,12 +27,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>全角色汇总统计</t>
-  </si>
-  <si>
-    <t>排名</t>
   </si>
   <si>
     <t>选手</t>
@@ -180,14 +177,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -643,148 +633,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1142,20 +1132,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F42"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <dimension ref="A1:E42"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="6" width="10" customWidth="1"/>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="5" width="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1171,813 +1160,690 @@
       <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="1" t="s">
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="1">
+        <v>27</v>
+      </c>
+      <c r="C3" s="1">
         <v>7</v>
       </c>
-      <c r="C3" s="1">
+      <c r="D3" s="1">
+        <v>34</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0.794117647058823</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="1">
+        <v>15</v>
+      </c>
+      <c r="C4" s="1">
+        <v>12</v>
+      </c>
+      <c r="D4" s="1">
         <v>27</v>
       </c>
-      <c r="D3" s="1">
+      <c r="E4" s="2">
+        <v>0.555555555555556</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="1">
+        <v>11</v>
+      </c>
+      <c r="C5" s="1">
+        <v>10</v>
+      </c>
+      <c r="D5" s="1">
+        <v>21</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0.523809523809524</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="1">
+        <v>10</v>
+      </c>
+      <c r="C6" s="1">
+        <v>8</v>
+      </c>
+      <c r="D6" s="1">
+        <v>18</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0.555555555555556</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="1">
+        <v>9</v>
+      </c>
+      <c r="C7" s="1">
         <v>7</v>
       </c>
-      <c r="E3" s="1">
-        <v>34</v>
-      </c>
-      <c r="F3" s="2">
-        <v>0.794117647058823</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="1">
+      <c r="D7" s="1">
+        <v>16</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0.5625</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="1">
+        <v>6</v>
+      </c>
+      <c r="C8" s="1">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1">
+        <v>9</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0.666666666666667</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="1">
+        <v>6</v>
+      </c>
+      <c r="C9" s="1">
+        <v>5</v>
+      </c>
+      <c r="D9" s="1">
+        <v>11</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0.545454545454545</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="1">
+        <v>6</v>
+      </c>
+      <c r="C10" s="1">
+        <v>17</v>
+      </c>
+      <c r="D10" s="1">
+        <v>23</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0.260869565217391</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="1">
+        <v>5</v>
+      </c>
+      <c r="C11" s="1">
+        <v>6</v>
+      </c>
+      <c r="D11" s="1">
+        <v>11</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0.454545454545454</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="1">
+      <c r="B12" s="1">
+        <v>5</v>
+      </c>
+      <c r="C12" s="1">
+        <v>7</v>
+      </c>
+      <c r="D12" s="1">
         <v>12</v>
       </c>
-      <c r="E4" s="1">
-        <v>27</v>
-      </c>
-      <c r="F4" s="2">
-        <v>0.555555555555556</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="1">
-        <v>11</v>
-      </c>
-      <c r="D5" s="1">
-        <v>10</v>
-      </c>
-      <c r="E5" s="1">
-        <v>21</v>
-      </c>
-      <c r="F5" s="2">
-        <v>0.523809523809524</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="1">
-        <v>10</v>
-      </c>
-      <c r="D6" s="1">
-        <v>8</v>
-      </c>
-      <c r="E6" s="1">
-        <v>18</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0.555555555555556</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="1">
+      <c r="E12" s="2">
+        <v>0.416666666666667</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="1">
         <v>5</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="1">
-        <v>9</v>
-      </c>
-      <c r="D7" s="1">
-        <v>7</v>
-      </c>
-      <c r="E7" s="1">
-        <v>16</v>
-      </c>
-      <c r="F7" s="2">
-        <v>0.5625</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="1">
-        <v>6</v>
-      </c>
-      <c r="D8" s="1">
-        <v>3</v>
-      </c>
-      <c r="E8" s="1">
-        <v>9</v>
-      </c>
-      <c r="F8" s="2">
-        <v>0.666666666666667</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="1">
-        <v>6</v>
-      </c>
-      <c r="D9" s="1">
-        <v>5</v>
-      </c>
-      <c r="E9" s="1">
-        <v>11</v>
-      </c>
-      <c r="F9" s="2">
-        <v>0.545454545454545</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="1">
-        <v>6</v>
-      </c>
-      <c r="D10" s="1">
-        <v>17</v>
-      </c>
-      <c r="E10" s="1">
-        <v>23</v>
-      </c>
-      <c r="F10" s="2">
-        <v>0.260869565217391</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="1">
-        <v>5</v>
-      </c>
-      <c r="D11" s="1">
-        <v>6</v>
-      </c>
-      <c r="E11" s="1">
-        <v>11</v>
-      </c>
-      <c r="F11" s="2">
-        <v>0.454545454545454</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="1">
-        <v>5</v>
-      </c>
-      <c r="D12" s="1">
-        <v>7</v>
-      </c>
-      <c r="E12" s="1">
-        <v>12</v>
-      </c>
-      <c r="F12" s="2">
-        <v>0.416666666666667</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="C13" s="1">
         <v>5</v>
       </c>
       <c r="D13" s="1">
+        <v>10</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="1">
         <v>5</v>
       </c>
-      <c r="E13" s="1">
+      <c r="C14" s="1">
+        <v>7</v>
+      </c>
+      <c r="D14" s="1">
+        <v>12</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0.416666666666667</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="1">
+        <v>4</v>
+      </c>
+      <c r="C15" s="1">
+        <v>0</v>
+      </c>
+      <c r="D15" s="1">
+        <v>4</v>
+      </c>
+      <c r="E15" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="1">
+        <v>4</v>
+      </c>
+      <c r="C16" s="1">
+        <v>6</v>
+      </c>
+      <c r="D16" s="1">
         <v>10</v>
       </c>
-      <c r="F13" s="2">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="1">
+      <c r="E16" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="1">
+        <v>4</v>
+      </c>
+      <c r="C17" s="1">
+        <v>2</v>
+      </c>
+      <c r="D17" s="1">
+        <v>6</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0.666666666666667</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" s="1">
+        <v>4</v>
+      </c>
+      <c r="C18" s="1">
+        <v>0</v>
+      </c>
+      <c r="D18" s="1">
+        <v>4</v>
+      </c>
+      <c r="E18" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="1">
+        <v>4</v>
+      </c>
+      <c r="C19" s="1">
+        <v>2</v>
+      </c>
+      <c r="D19" s="1">
+        <v>6</v>
+      </c>
+      <c r="E19" s="2">
+        <v>0.666666666666667</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" s="1">
+        <v>4</v>
+      </c>
+      <c r="C20" s="1">
         <v>5</v>
       </c>
-      <c r="D14" s="1">
+      <c r="D20" s="1">
+        <v>9</v>
+      </c>
+      <c r="E20" s="2">
+        <v>0.444444444444444</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21" s="1">
+        <v>4</v>
+      </c>
+      <c r="C21" s="1">
+        <v>3</v>
+      </c>
+      <c r="D21" s="1">
         <v>7</v>
       </c>
-      <c r="E14" s="1">
-        <v>12</v>
-      </c>
-      <c r="F14" s="2">
-        <v>0.416666666666667</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="1">
-        <v>13</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15" s="1">
-        <v>4</v>
-      </c>
-      <c r="D15" s="1">
-        <v>0</v>
-      </c>
-      <c r="E15" s="1">
-        <v>4</v>
-      </c>
-      <c r="F15" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="1">
-        <v>14</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" s="1">
-        <v>4</v>
-      </c>
-      <c r="D16" s="1">
-        <v>6</v>
-      </c>
-      <c r="E16" s="1">
-        <v>10</v>
-      </c>
-      <c r="F16" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="1">
-        <v>15</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17" s="1">
-        <v>4</v>
-      </c>
-      <c r="D17" s="1">
-        <v>2</v>
-      </c>
-      <c r="E17" s="1">
-        <v>6</v>
-      </c>
-      <c r="F17" s="2">
-        <v>0.666666666666667</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="1">
-        <v>16</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" s="1">
-        <v>4</v>
-      </c>
-      <c r="D18" s="1">
-        <v>0</v>
-      </c>
-      <c r="E18" s="1">
-        <v>4</v>
-      </c>
-      <c r="F18" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="1">
-        <v>17</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C19" s="1">
-        <v>4</v>
-      </c>
-      <c r="D19" s="1">
-        <v>2</v>
-      </c>
-      <c r="E19" s="1">
-        <v>6</v>
-      </c>
-      <c r="F19" s="2">
-        <v>0.666666666666667</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" s="1">
-        <v>18</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C20" s="1">
-        <v>4</v>
-      </c>
-      <c r="D20" s="1">
+      <c r="E21" s="2">
+        <v>0.571428571428571</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" s="1">
+        <v>3</v>
+      </c>
+      <c r="C22" s="1">
         <v>5</v>
       </c>
-      <c r="E20" s="1">
-        <v>9</v>
-      </c>
-      <c r="F20" s="2">
-        <v>0.444444444444444</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="1">
-        <v>19</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C21" s="1">
-        <v>4</v>
-      </c>
-      <c r="D21" s="1">
+      <c r="D22" s="1">
+        <v>8</v>
+      </c>
+      <c r="E22" s="2">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" s="1">
         <v>3</v>
-      </c>
-      <c r="E21" s="1">
-        <v>7</v>
-      </c>
-      <c r="F21" s="2">
-        <v>0.571428571428571</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22" s="1">
-        <v>20</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C22" s="1">
-        <v>3</v>
-      </c>
-      <c r="D22" s="1">
-        <v>5</v>
-      </c>
-      <c r="E22" s="1">
-        <v>8</v>
-      </c>
-      <c r="F22" s="2">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23" s="1">
-        <v>21</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="C23" s="1">
         <v>3</v>
       </c>
       <c r="D23" s="1">
+        <v>6</v>
+      </c>
+      <c r="E23" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24" s="1">
+        <v>2</v>
+      </c>
+      <c r="C24" s="1">
+        <v>1</v>
+      </c>
+      <c r="D24" s="1">
         <v>3</v>
       </c>
-      <c r="E23" s="1">
-        <v>6</v>
-      </c>
-      <c r="F23" s="2">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24" s="1">
-        <v>22</v>
-      </c>
-      <c r="B24" s="1" t="s">
+      <c r="E24" s="2">
+        <v>0.666666666666667</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C24" s="1">
+      <c r="B25" s="1">
         <v>2</v>
-      </c>
-      <c r="D24" s="1">
-        <v>1</v>
-      </c>
-      <c r="E24" s="1">
-        <v>3</v>
-      </c>
-      <c r="F24" s="2">
-        <v>0.666666666666667</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25" s="1">
-        <v>23</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>29</v>
       </c>
       <c r="C25" s="1">
         <v>2</v>
       </c>
       <c r="D25" s="1">
+        <v>4</v>
+      </c>
+      <c r="E25" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B26" s="1">
         <v>2</v>
       </c>
-      <c r="E25" s="1">
+      <c r="C26" s="1">
         <v>4</v>
       </c>
-      <c r="F25" s="2">
+      <c r="D26" s="1">
+        <v>6</v>
+      </c>
+      <c r="E26" s="2">
+        <v>0.333333333333333</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B27" s="1">
+        <v>2</v>
+      </c>
+      <c r="C27" s="1">
+        <v>3</v>
+      </c>
+      <c r="D27" s="1">
+        <v>5</v>
+      </c>
+      <c r="E27" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B28" s="1">
+        <v>2</v>
+      </c>
+      <c r="C28" s="1">
+        <v>1</v>
+      </c>
+      <c r="D28" s="1">
+        <v>3</v>
+      </c>
+      <c r="E28" s="2">
+        <v>0.666666666666667</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B29" s="1">
+        <v>1</v>
+      </c>
+      <c r="C29" s="1">
+        <v>0</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1</v>
+      </c>
+      <c r="E29" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30" s="1">
+        <v>1</v>
+      </c>
+      <c r="C30" s="1">
+        <v>1</v>
+      </c>
+      <c r="D30" s="1">
+        <v>2</v>
+      </c>
+      <c r="E30" s="2">
         <v>0.5</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
-      <c r="A26" s="1">
-        <v>24</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C26" s="1">
+    <row r="31" spans="1:5">
+      <c r="A31" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B31" s="1">
+        <v>1</v>
+      </c>
+      <c r="C31" s="1">
+        <v>0</v>
+      </c>
+      <c r="D31" s="1">
+        <v>1</v>
+      </c>
+      <c r="E31" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B32" s="1">
+        <v>1</v>
+      </c>
+      <c r="C32" s="1">
+        <v>1</v>
+      </c>
+      <c r="D32" s="1">
         <v>2</v>
       </c>
-      <c r="D26" s="1">
+      <c r="E32" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B33" s="1">
+        <v>1</v>
+      </c>
+      <c r="C33" s="1">
         <v>4</v>
       </c>
-      <c r="E26" s="1">
-        <v>6</v>
-      </c>
-      <c r="F26" s="2">
-        <v>0.333333333333333</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27" s="1">
-        <v>25</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C27" s="1">
-        <v>2</v>
-      </c>
-      <c r="D27" s="1">
+      <c r="D33" s="1">
+        <v>5</v>
+      </c>
+      <c r="E33" s="2">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" s="1">
+        <v>1</v>
+      </c>
+      <c r="C34" s="1">
+        <v>4</v>
+      </c>
+      <c r="D34" s="1">
+        <v>5</v>
+      </c>
+      <c r="E34" s="2">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" s="1">
+        <v>1</v>
+      </c>
+      <c r="C35" s="1">
+        <v>9</v>
+      </c>
+      <c r="D35" s="1">
+        <v>10</v>
+      </c>
+      <c r="E35" s="2">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36" s="1">
+        <v>0</v>
+      </c>
+      <c r="C36" s="1">
         <v>3</v>
-      </c>
-      <c r="E27" s="1">
-        <v>5</v>
-      </c>
-      <c r="F27" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28" s="1">
-        <v>26</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C28" s="1">
-        <v>2</v>
-      </c>
-      <c r="D28" s="1">
-        <v>1</v>
-      </c>
-      <c r="E28" s="1">
-        <v>3</v>
-      </c>
-      <c r="F28" s="2">
-        <v>0.666666666666667</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29" s="1">
-        <v>27</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C29" s="1">
-        <v>1</v>
-      </c>
-      <c r="D29" s="1">
-        <v>0</v>
-      </c>
-      <c r="E29" s="1">
-        <v>1</v>
-      </c>
-      <c r="F29" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30" s="1">
-        <v>28</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C30" s="1">
-        <v>1</v>
-      </c>
-      <c r="D30" s="1">
-        <v>1</v>
-      </c>
-      <c r="E30" s="1">
-        <v>2</v>
-      </c>
-      <c r="F30" s="2">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31" s="1">
-        <v>29</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C31" s="1">
-        <v>1</v>
-      </c>
-      <c r="D31" s="1">
-        <v>0</v>
-      </c>
-      <c r="E31" s="1">
-        <v>1</v>
-      </c>
-      <c r="F31" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32" s="1">
-        <v>30</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C32" s="1">
-        <v>1</v>
-      </c>
-      <c r="D32" s="1">
-        <v>1</v>
-      </c>
-      <c r="E32" s="1">
-        <v>2</v>
-      </c>
-      <c r="F32" s="2">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33" s="1">
-        <v>31</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C33" s="1">
-        <v>1</v>
-      </c>
-      <c r="D33" s="1">
-        <v>4</v>
-      </c>
-      <c r="E33" s="1">
-        <v>5</v>
-      </c>
-      <c r="F33" s="2">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34" s="1">
-        <v>32</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C34" s="1">
-        <v>1</v>
-      </c>
-      <c r="D34" s="1">
-        <v>4</v>
-      </c>
-      <c r="E34" s="1">
-        <v>5</v>
-      </c>
-      <c r="F34" s="2">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35" s="1">
-        <v>33</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C35" s="1">
-        <v>1</v>
-      </c>
-      <c r="D35" s="1">
-        <v>9</v>
-      </c>
-      <c r="E35" s="1">
-        <v>10</v>
-      </c>
-      <c r="F35" s="2">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36" s="1">
-        <v>34</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C36" s="1">
-        <v>0</v>
       </c>
       <c r="D36" s="1">
         <v>3</v>
       </c>
-      <c r="E36" s="1">
-        <v>3</v>
-      </c>
-      <c r="F36" s="2">
+      <c r="E36" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:6">
-      <c r="A37" s="1">
-        <v>35</v>
-      </c>
-      <c r="B37" s="1" t="s">
+    <row r="37" spans="1:5">
+      <c r="A37" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" s="1">
+        <v>0</v>
+      </c>
+      <c r="C37" s="1">
+        <v>1</v>
+      </c>
+      <c r="D37" s="1">
+        <v>1</v>
+      </c>
+      <c r="E37" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C37" s="1">
+      <c r="B38" s="1">
         <v>0</v>
       </c>
-      <c r="D37" s="1">
-        <v>1</v>
-      </c>
-      <c r="E37" s="1">
-        <v>1</v>
-      </c>
-      <c r="F37" s="2">
+      <c r="C38" s="1">
+        <v>1</v>
+      </c>
+      <c r="D38" s="1">
+        <v>1</v>
+      </c>
+      <c r="E38" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:6">
-      <c r="A38" s="1">
-        <v>36</v>
-      </c>
-      <c r="B38" s="1" t="s">
+    <row r="39" spans="1:5">
+      <c r="A39" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C38" s="1">
+      <c r="B39" s="1">
         <v>0</v>
       </c>
-      <c r="D38" s="1">
-        <v>1</v>
-      </c>
-      <c r="E38" s="1">
-        <v>1</v>
-      </c>
-      <c r="F38" s="2">
+      <c r="C39" s="1">
+        <v>1</v>
+      </c>
+      <c r="D39" s="1">
+        <v>1</v>
+      </c>
+      <c r="E39" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:6">
-      <c r="A39" s="1">
-        <v>37</v>
-      </c>
-      <c r="B39" s="1" t="s">
+    <row r="40" spans="1:5">
+      <c r="A40" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C39" s="1">
+      <c r="B40" s="1">
         <v>0</v>
       </c>
-      <c r="D39" s="1">
-        <v>1</v>
-      </c>
-      <c r="E39" s="1">
-        <v>1</v>
-      </c>
-      <c r="F39" s="2">
+      <c r="C40" s="1">
+        <v>1</v>
+      </c>
+      <c r="D40" s="1">
+        <v>1</v>
+      </c>
+      <c r="E40" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:6">
-      <c r="A40" s="1">
-        <v>38</v>
-      </c>
-      <c r="B40" s="1" t="s">
+    <row r="41" spans="1:5">
+      <c r="A41" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C40" s="1">
+      <c r="B41" s="1">
         <v>0</v>
       </c>
-      <c r="D40" s="1">
-        <v>1</v>
-      </c>
-      <c r="E40" s="1">
-        <v>1</v>
-      </c>
-      <c r="F40" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41" s="1">
-        <v>39</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>45</v>
-      </c>
       <c r="C41" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D41" s="1">
         <v>2</v>
       </c>
-      <c r="E41" s="1">
-        <v>2</v>
-      </c>
-      <c r="F41" s="2">
+      <c r="E41" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
-      <c r="A42" s="1">
-        <v>40</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>46</v>
+    <row r="42" spans="1:5">
+      <c r="A42" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42" s="1">
+        <v>0</v>
       </c>
       <c r="C42" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D42" s="1">
         <v>8</v>
       </c>
-      <c r="E42" s="1">
-        <v>8</v>
-      </c>
-      <c r="F42" s="2">
+      <c r="E42" s="2">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
